--- a/artfynd/A 29197-2022 artfynd.xlsx
+++ b/artfynd/A 29197-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124027520</v>
+        <v>124028359</v>
       </c>
       <c r="B2" t="n">
-        <v>58351</v>
+        <v>56449</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124028359</v>
+        <v>124027520</v>
       </c>
       <c r="B3" t="n">
-        <v>56449</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,24 +803,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29197-2022 artfynd.xlsx
+++ b/artfynd/A 29197-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124028359</v>
+        <v>124027520</v>
       </c>
       <c r="B2" t="n">
-        <v>56449</v>
+        <v>58351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124027520</v>
+        <v>124028359</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>56449</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,33 +812,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29197-2022 artfynd.xlsx
+++ b/artfynd/A 29197-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124028359</v>
+        <v>124027520</v>
       </c>
       <c r="B2" t="n">
-        <v>56471</v>
+        <v>58373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124027520</v>
+        <v>124028359</v>
       </c>
       <c r="B3" t="n">
-        <v>58373</v>
+        <v>56471</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,33 +812,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29197-2022 artfynd.xlsx
+++ b/artfynd/A 29197-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124027520</v>
+        <v>124028359</v>
       </c>
       <c r="B2" t="n">
-        <v>58373</v>
+        <v>56471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>208255</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124028359</v>
+        <v>124027520</v>
       </c>
       <c r="B3" t="n">
-        <v>56471</v>
+        <v>58373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,24 +803,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ersbo etapp syd, Gstr</t>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
